--- a/TAU5 - Flameproof Certificate List V0.7 (17.09.2025).xlsx
+++ b/TAU5 - Flameproof Certificate List V0.7 (17.09.2025).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harms\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harms\Desktop\CH_FILES\Development\dms_demo_tau5\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A3E249-0649-4584-ADCB-7E1A99251648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E136D360-F207-4917-9849-3C7DAC6348E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flameproof Certificates" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>File Name</t>
   </si>
@@ -95,12 +95,45 @@
   <si>
     <t>Date</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ComplianceHub</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Flameproof Certificate List</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,8 +180,22 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -160,6 +207,16 @@
         <fgColor rgb="FF002060"/>
         <bgColor indexed="64"/>
       </patternFill>
+    </fill>
+    <fill>
+      <gradientFill>
+        <stop position="0">
+          <color theme="1"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FF002060"/>
+        </stop>
+      </gradientFill>
     </fill>
   </fills>
   <borders count="4">
@@ -213,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
@@ -242,6 +299,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -262,156 +323,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>9524</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>673200</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Rectangle 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CADB7055-7B4A-4A7A-8C7E-7876A602BFF5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="149087" y="149087"/>
-          <a:ext cx="17005437" cy="673200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:gradFill flip="none" rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="tx1"/>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:srgbClr val="002060"/>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="0" scaled="1"/>
-          <a:tileRect/>
-        </a:gradFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="2000" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>ComplianceHub</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Flameproof Certificate List</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1200" b="1">
-            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>124239</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>66261</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>590296</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>580611</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA0D4D6B-01DF-4D45-A4D8-A7CA30FE1361}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="273326" y="215348"/>
-          <a:ext cx="466057" cy="514350"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -688,7 +599,18 @@
     <col min="10" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="53.45" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:9" ht="53.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+    </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
         <v>0</v>
@@ -46826,6 +46748,9 @@
       <c r="I4615" s="7"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -46834,7 +46759,6 @@
     <oddHeader>&amp;A</oddHeader>
     <oddFooter>&amp;L&amp;B Confidential&amp;B&amp;C&amp;D&amp;RPage &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -46892,7 +46816,7 @@
       </c>
       <c r="D2" s="9">
         <f ca="1">TODAY()</f>
-        <v>45917</v>
+        <v>46121</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
